--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -780,49 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130127001</v>
+        <v>130126991</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490826</v>
+        <v>490910</v>
       </c>
       <c r="R3" t="n">
-        <v>6679443</v>
+        <v>6679466</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +864,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130127009</v>
+        <v>130127001</v>
       </c>
       <c r="B4" t="n">
         <v>98831</v>
@@ -926,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490956</v>
+        <v>490826</v>
       </c>
       <c r="R4" t="n">
-        <v>6679462</v>
+        <v>6679443</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +961,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,45 +989,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130126991</v>
+        <v>130127009</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>98831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490910</v>
+        <v>490956</v>
       </c>
       <c r="R5" t="n">
-        <v>6679466</v>
+        <v>6679462</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,6 +1077,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B23" t="n">
-        <v>91623</v>
+        <v>80200</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R23" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B24" t="n">
-        <v>80200</v>
+        <v>91623</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R24" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130127005</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,45 +780,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130126991</v>
+        <v>130127001</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490910</v>
+        <v>490826</v>
       </c>
       <c r="R3" t="n">
-        <v>6679466</v>
+        <v>6679443</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,7 +859,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130127001</v>
+        <v>130127009</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490826</v>
+        <v>490956</v>
       </c>
       <c r="R4" t="n">
-        <v>6679443</v>
+        <v>6679462</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,7 +966,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,49 +994,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130127009</v>
+        <v>130126991</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490956</v>
+        <v>490910</v>
       </c>
       <c r="R5" t="n">
-        <v>6679462</v>
+        <v>6679466</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,7 +1069,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>130126999</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>130127010</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>130127002</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>130127003</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>130126987</v>
       </c>
       <c r="B17" t="n">
-        <v>91623</v>
+        <v>91625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>130127000</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>130127011</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>130127004</v>
       </c>
       <c r="B20" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>130126986</v>
       </c>
       <c r="B24" t="n">
-        <v>91623</v>
+        <v>91625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130127007</v>
       </c>
       <c r="B25" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>130126998</v>
       </c>
       <c r="B26" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130127005</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,49 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130127001</v>
+        <v>130126991</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490826</v>
+        <v>490910</v>
       </c>
       <c r="R3" t="n">
-        <v>6679443</v>
+        <v>6679466</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +864,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130127009</v>
+        <v>130127001</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490956</v>
+        <v>490826</v>
       </c>
       <c r="R4" t="n">
-        <v>6679462</v>
+        <v>6679443</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +961,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,45 +989,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130126991</v>
+        <v>130127009</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490910</v>
+        <v>490956</v>
       </c>
       <c r="R5" t="n">
-        <v>6679466</v>
+        <v>6679462</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,6 +1077,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>130126999</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>130126985</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>130127013</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>130126984</v>
       </c>
       <c r="B9" t="n">
-        <v>56314</v>
+        <v>56399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>130126989</v>
       </c>
       <c r="B10" t="n">
-        <v>80228</v>
+        <v>80313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,53 +1596,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130127012</v>
+        <v>130126995</v>
       </c>
       <c r="B11" t="n">
-        <v>56922</v>
+        <v>80245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490767</v>
+        <v>490815</v>
       </c>
       <c r="R11" t="n">
-        <v>6679313</v>
+        <v>6679423</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1675,11 +1667,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1706,45 +1693,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130126995</v>
+        <v>130127012</v>
       </c>
       <c r="B12" t="n">
-        <v>80160</v>
+        <v>57007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490815</v>
+        <v>490767</v>
       </c>
       <c r="R12" t="n">
-        <v>6679423</v>
+        <v>6679313</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1777,6 +1772,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,7 +1806,7 @@
         <v>130127010</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>130127002</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>130127003</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>130126979</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>130126987</v>
       </c>
       <c r="B17" t="n">
-        <v>91625</v>
+        <v>91712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>130127000</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>130127011</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>130127004</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>130126983</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>130126994</v>
       </c>
       <c r="B22" t="n">
-        <v>80160</v>
+        <v>80245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B23" t="n">
-        <v>80200</v>
+        <v>91712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R23" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B24" t="n">
-        <v>91625</v>
+        <v>80285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R24" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,7 +3061,7 @@
         <v>130127007</v>
       </c>
       <c r="B25" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>130126998</v>
       </c>
       <c r="B26" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>130136460</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -780,45 +780,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130126991</v>
+        <v>130127009</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490910</v>
+        <v>490956</v>
       </c>
       <c r="R3" t="n">
-        <v>6679466</v>
+        <v>6679462</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,7 +859,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -989,49 +994,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130127009</v>
+        <v>130126991</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490956</v>
+        <v>490910</v>
       </c>
       <c r="R5" t="n">
-        <v>6679462</v>
+        <v>6679466</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,7 +1069,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1596,45 +1596,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130126995</v>
+        <v>130127012</v>
       </c>
       <c r="B11" t="n">
-        <v>80245</v>
+        <v>57007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490815</v>
+        <v>490767</v>
       </c>
       <c r="R11" t="n">
-        <v>6679423</v>
+        <v>6679313</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1667,6 +1675,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,53 +1706,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130127012</v>
+        <v>130126995</v>
       </c>
       <c r="B12" t="n">
-        <v>57007</v>
+        <v>80245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490767</v>
+        <v>490815</v>
       </c>
       <c r="R12" t="n">
-        <v>6679313</v>
+        <v>6679423</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1772,11 +1777,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,7 +1803,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130127010</v>
+        <v>130127002</v>
       </c>
       <c r="B13" t="n">
         <v>98920</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490952</v>
+        <v>490831</v>
       </c>
       <c r="R13" t="n">
-        <v>6679459</v>
+        <v>6679493</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>1 bladrosett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1910,7 +1910,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130127002</v>
+        <v>130127010</v>
       </c>
       <c r="B14" t="n">
         <v>98920</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490831</v>
+        <v>490952</v>
       </c>
       <c r="R14" t="n">
-        <v>6679493</v>
+        <v>6679459</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1 bladrosett.</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127000</v>
+        <v>130127011</v>
       </c>
       <c r="B18" t="n">
         <v>98920</v>
@@ -2364,14 +2364,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490811</v>
+        <v>491011</v>
       </c>
       <c r="R18" t="n">
-        <v>6679375</v>
+        <v>6679350</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,7 +2417,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2436,7 +2435,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130127011</v>
+        <v>130127000</v>
       </c>
       <c r="B19" t="n">
         <v>98920</v>
@@ -2471,14 +2470,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491011</v>
+        <v>490811</v>
       </c>
       <c r="R19" t="n">
-        <v>6679350</v>
+        <v>6679375</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,7 +2514,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter</t>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,6 +2523,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B23" t="n">
-        <v>91712</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R23" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>91712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R24" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -780,49 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130127009</v>
+        <v>130126991</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490956</v>
+        <v>490910</v>
       </c>
       <c r="R3" t="n">
-        <v>6679462</v>
+        <v>6679466</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,7 +855,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +864,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -994,45 +989,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130126991</v>
+        <v>130127009</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490910</v>
+        <v>490956</v>
       </c>
       <c r="R5" t="n">
-        <v>6679466</v>
+        <v>6679462</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,6 +1077,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1803,7 +1803,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130127002</v>
+        <v>130127010</v>
       </c>
       <c r="B13" t="n">
         <v>98920</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490831</v>
+        <v>490952</v>
       </c>
       <c r="R13" t="n">
-        <v>6679493</v>
+        <v>6679459</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 bladrosett.</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1910,7 +1910,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130127010</v>
+        <v>130127002</v>
       </c>
       <c r="B14" t="n">
         <v>98920</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490952</v>
+        <v>490831</v>
       </c>
       <c r="R14" t="n">
-        <v>6679459</v>
+        <v>6679493</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>1 bladrosett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127011</v>
+        <v>130127000</v>
       </c>
       <c r="B18" t="n">
         <v>98920</v>
@@ -2364,14 +2364,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491011</v>
+        <v>490811</v>
       </c>
       <c r="R18" t="n">
-        <v>6679350</v>
+        <v>6679375</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter</t>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,6 +2417,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2435,7 +2436,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130127000</v>
+        <v>130127011</v>
       </c>
       <c r="B19" t="n">
         <v>98920</v>
@@ -2470,14 +2471,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490811</v>
+        <v>491011</v>
       </c>
       <c r="R19" t="n">
-        <v>6679375</v>
+        <v>6679350</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2514,7 +2515,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,7 +2524,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2647,53 +2647,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130126983</v>
+        <v>130126994</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>80245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490692</v>
+        <v>490798</v>
       </c>
       <c r="R21" t="n">
-        <v>6679308</v>
+        <v>6679401</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2726,11 +2718,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2757,45 +2744,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130126994</v>
+        <v>130126983</v>
       </c>
       <c r="B22" t="n">
-        <v>80245</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490798</v>
+        <v>490692</v>
       </c>
       <c r="R22" t="n">
-        <v>6679401</v>
+        <v>6679308</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2828,6 +2823,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>91712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R23" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B24" t="n">
-        <v>91712</v>
+        <v>80285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R24" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3058,7 +3058,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130127007</v>
+        <v>130126998</v>
       </c>
       <c r="B25" t="n">
         <v>98920</v>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490905</v>
+        <v>490732</v>
       </c>
       <c r="R25" t="n">
-        <v>6679465</v>
+        <v>6679370</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>15-tal</t>
+          <t>25-tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,7 +3163,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130126998</v>
+        <v>130127007</v>
       </c>
       <c r="B26" t="n">
         <v>98920</v>
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490732</v>
+        <v>490905</v>
       </c>
       <c r="R26" t="n">
-        <v>6679370</v>
+        <v>6679465</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter.</t>
+          <t>15-tal</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -780,45 +780,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130126991</v>
+        <v>130127001</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490910</v>
+        <v>490826</v>
       </c>
       <c r="R3" t="n">
-        <v>6679466</v>
+        <v>6679443</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,7 +859,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130127001</v>
+        <v>130127009</v>
       </c>
       <c r="B4" t="n">
         <v>98920</v>
@@ -921,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490826</v>
+        <v>490956</v>
       </c>
       <c r="R4" t="n">
-        <v>6679443</v>
+        <v>6679462</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,7 +966,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,49 +994,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130127009</v>
+        <v>130126991</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>8451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490956</v>
+        <v>490910</v>
       </c>
       <c r="R5" t="n">
-        <v>6679462</v>
+        <v>6679466</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,7 +1069,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1596,53 +1596,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130127012</v>
+        <v>130126995</v>
       </c>
       <c r="B11" t="n">
-        <v>57007</v>
+        <v>80245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490767</v>
+        <v>490815</v>
       </c>
       <c r="R11" t="n">
-        <v>6679313</v>
+        <v>6679423</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1675,11 +1667,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1706,45 +1693,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130126995</v>
+        <v>130127012</v>
       </c>
       <c r="B12" t="n">
-        <v>80245</v>
+        <v>57007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490815</v>
+        <v>490767</v>
       </c>
       <c r="R12" t="n">
-        <v>6679423</v>
+        <v>6679313</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1777,6 +1772,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2232,45 +2232,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130126987</v>
+        <v>130127000</v>
       </c>
       <c r="B17" t="n">
-        <v>91712</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490761</v>
+        <v>490811</v>
       </c>
       <c r="R17" t="n">
-        <v>6679321</v>
+        <v>6679375</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2305,12 +2309,18 @@
           <t>2025-12-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2339,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127000</v>
+        <v>130127011</v>
       </c>
       <c r="B18" t="n">
         <v>98920</v>
@@ -2364,14 +2374,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490811</v>
+        <v>491011</v>
       </c>
       <c r="R18" t="n">
-        <v>6679375</v>
+        <v>6679350</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2408,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,7 +2427,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2436,49 +2445,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130127011</v>
+        <v>130126987</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>91712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491011</v>
+        <v>490761</v>
       </c>
       <c r="R19" t="n">
-        <v>6679350</v>
+        <v>6679321</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,11 +2516,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,45 +2647,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130126994</v>
+        <v>130126983</v>
       </c>
       <c r="B21" t="n">
-        <v>80245</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490798</v>
+        <v>490692</v>
       </c>
       <c r="R21" t="n">
-        <v>6679401</v>
+        <v>6679308</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2718,6 +2726,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2744,53 +2757,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130126983</v>
+        <v>130126994</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>80245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490692</v>
+        <v>490798</v>
       </c>
       <c r="R22" t="n">
-        <v>6679308</v>
+        <v>6679401</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2823,11 +2828,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B23" t="n">
-        <v>91712</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R23" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>91712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R24" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3058,7 +3058,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130126998</v>
+        <v>130127007</v>
       </c>
       <c r="B25" t="n">
         <v>98920</v>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490732</v>
+        <v>490905</v>
       </c>
       <c r="R25" t="n">
-        <v>6679370</v>
+        <v>6679465</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter.</t>
+          <t>15-tal</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,7 +3163,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130127007</v>
+        <v>130126998</v>
       </c>
       <c r="B26" t="n">
         <v>98920</v>
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490905</v>
+        <v>490732</v>
       </c>
       <c r="R26" t="n">
-        <v>6679465</v>
+        <v>6679370</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>15-tal</t>
+          <t>25-tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -2232,49 +2232,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130127000</v>
+        <v>130126987</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>91712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490811</v>
+        <v>490761</v>
       </c>
       <c r="R17" t="n">
-        <v>6679375</v>
+        <v>6679321</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2309,18 +2305,12 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2339,7 +2329,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127011</v>
+        <v>130127000</v>
       </c>
       <c r="B18" t="n">
         <v>98920</v>
@@ -2374,14 +2364,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491011</v>
+        <v>490811</v>
       </c>
       <c r="R18" t="n">
-        <v>6679350</v>
+        <v>6679375</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2418,7 +2408,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter</t>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,6 +2417,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2445,45 +2436,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130126987</v>
+        <v>130127011</v>
       </c>
       <c r="B19" t="n">
-        <v>91712</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490761</v>
+        <v>491011</v>
       </c>
       <c r="R19" t="n">
-        <v>6679321</v>
+        <v>6679350</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2516,6 +2511,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,45 +2647,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130126994</v>
+        <v>130126983</v>
       </c>
       <c r="B21" t="n">
-        <v>80245</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490798</v>
+        <v>490692</v>
       </c>
       <c r="R21" t="n">
-        <v>6679401</v>
+        <v>6679308</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2718,6 +2726,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2744,53 +2757,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130126983</v>
+        <v>130126994</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>80245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490692</v>
+        <v>490798</v>
       </c>
       <c r="R22" t="n">
-        <v>6679308</v>
+        <v>6679401</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2823,11 +2828,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B23" t="n">
-        <v>91712</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R23" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>91712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R24" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -2232,45 +2232,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130126987</v>
+        <v>130127000</v>
       </c>
       <c r="B17" t="n">
-        <v>91712</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490761</v>
+        <v>490811</v>
       </c>
       <c r="R17" t="n">
-        <v>6679321</v>
+        <v>6679375</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2305,12 +2309,18 @@
           <t>2025-12-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2329,7 +2339,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127000</v>
+        <v>130127011</v>
       </c>
       <c r="B18" t="n">
         <v>98920</v>
@@ -2364,14 +2374,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490811</v>
+        <v>491011</v>
       </c>
       <c r="R18" t="n">
-        <v>6679375</v>
+        <v>6679350</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2408,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,7 +2427,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2436,49 +2445,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130127011</v>
+        <v>130126987</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>91712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491011</v>
+        <v>490761</v>
       </c>
       <c r="R19" t="n">
-        <v>6679350</v>
+        <v>6679321</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,11 +2516,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,53 +2647,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130126983</v>
+        <v>130126994</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>80245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490692</v>
+        <v>490798</v>
       </c>
       <c r="R21" t="n">
-        <v>6679308</v>
+        <v>6679401</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2726,11 +2718,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2757,45 +2744,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130126994</v>
+        <v>130126983</v>
       </c>
       <c r="B22" t="n">
-        <v>80245</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490798</v>
+        <v>490692</v>
       </c>
       <c r="R22" t="n">
-        <v>6679401</v>
+        <v>6679308</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2828,6 +2823,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130127005</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>130127001</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>130127009</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>130126999</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>130126985</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>130127013</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>130126989</v>
       </c>
       <c r="B10" t="n">
-        <v>80313</v>
+        <v>80316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,45 +1596,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130126995</v>
+        <v>130127012</v>
       </c>
       <c r="B11" t="n">
-        <v>80245</v>
+        <v>57007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490815</v>
+        <v>490767</v>
       </c>
       <c r="R11" t="n">
-        <v>6679423</v>
+        <v>6679313</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1667,6 +1675,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,53 +1706,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130127012</v>
+        <v>130126995</v>
       </c>
       <c r="B12" t="n">
-        <v>57007</v>
+        <v>80248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490767</v>
+        <v>490815</v>
       </c>
       <c r="R12" t="n">
-        <v>6679313</v>
+        <v>6679423</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1772,11 +1777,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130127002</v>
+        <v>130127010</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490831</v>
+        <v>490952</v>
       </c>
       <c r="R13" t="n">
-        <v>6679493</v>
+        <v>6679459</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 bladrosett.</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1910,10 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130127010</v>
+        <v>130127002</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490952</v>
+        <v>490831</v>
       </c>
       <c r="R14" t="n">
-        <v>6679459</v>
+        <v>6679493</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>1 bladrosett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,7 +2020,7 @@
         <v>130127003</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,49 +2232,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130127000</v>
+        <v>130126987</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>91715</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490811</v>
+        <v>490761</v>
       </c>
       <c r="R17" t="n">
-        <v>6679375</v>
+        <v>6679321</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2309,18 +2305,12 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2339,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127011</v>
+        <v>130127000</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,14 +2364,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491011</v>
+        <v>490811</v>
       </c>
       <c r="R18" t="n">
-        <v>6679350</v>
+        <v>6679375</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2418,7 +2408,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter</t>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,6 +2417,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2445,45 +2436,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130126987</v>
+        <v>130127011</v>
       </c>
       <c r="B19" t="n">
-        <v>91712</v>
+        <v>98923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490761</v>
+        <v>491011</v>
       </c>
       <c r="R19" t="n">
-        <v>6679321</v>
+        <v>6679350</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2516,6 +2511,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,7 +2545,7 @@
         <v>130127004</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,45 +2647,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130126994</v>
+        <v>130126983</v>
       </c>
       <c r="B21" t="n">
-        <v>80245</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490798</v>
+        <v>490692</v>
       </c>
       <c r="R21" t="n">
-        <v>6679401</v>
+        <v>6679308</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2718,6 +2726,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2744,53 +2757,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130126983</v>
+        <v>130126994</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>80248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490692</v>
+        <v>490798</v>
       </c>
       <c r="R22" t="n">
-        <v>6679308</v>
+        <v>6679401</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2823,11 +2828,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>91715</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R23" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B24" t="n">
-        <v>91712</v>
+        <v>80288</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R24" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,7 +3061,7 @@
         <v>130127007</v>
       </c>
       <c r="B25" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>130126998</v>
       </c>
       <c r="B26" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130127005</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130127001</v>
+        <v>130127009</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490826</v>
+        <v>490956</v>
       </c>
       <c r="R4" t="n">
-        <v>6679443</v>
+        <v>6679462</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130127009</v>
+        <v>130127001</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490956</v>
+        <v>490826</v>
       </c>
       <c r="R5" t="n">
-        <v>6679462</v>
+        <v>6679443</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1099,7 @@
         <v>130126999</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>130126985</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>130127013</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>130126984</v>
       </c>
       <c r="B9" t="n">
-        <v>56399</v>
+        <v>56425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>130126989</v>
       </c>
       <c r="B10" t="n">
-        <v>80316</v>
+        <v>80342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130127012</v>
       </c>
       <c r="B11" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>130126995</v>
       </c>
       <c r="B12" t="n">
-        <v>80248</v>
+        <v>80274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>130127010</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>130127002</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>130127003</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>130126979</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>130126987</v>
       </c>
       <c r="B17" t="n">
-        <v>91715</v>
+        <v>91741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127000</v>
+        <v>130127011</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490811</v>
+        <v>491011</v>
       </c>
       <c r="R18" t="n">
-        <v>6679375</v>
+        <v>6679350</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,7 +2417,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2436,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130127011</v>
+        <v>130127000</v>
       </c>
       <c r="B19" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,14 +2470,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491011</v>
+        <v>490811</v>
       </c>
       <c r="R19" t="n">
-        <v>6679350</v>
+        <v>6679375</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,7 +2514,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter</t>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,6 +2523,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>130127004</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>130126983</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>130126994</v>
       </c>
       <c r="B22" t="n">
-        <v>80248</v>
+        <v>80274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126986</v>
+        <v>130126993</v>
       </c>
       <c r="B23" t="n">
-        <v>91715</v>
+        <v>80314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490770</v>
+        <v>490802</v>
       </c>
       <c r="R23" t="n">
-        <v>6679323</v>
+        <v>6679402</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,32 +2956,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126993</v>
+        <v>130126986</v>
       </c>
       <c r="B24" t="n">
-        <v>80288</v>
+        <v>91741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490802</v>
+        <v>490770</v>
       </c>
       <c r="R24" t="n">
-        <v>6679402</v>
+        <v>6679323</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,7 +3061,7 @@
         <v>130127007</v>
       </c>
       <c r="B25" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>130126998</v>
       </c>
       <c r="B26" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>130136460</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -780,45 +780,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130126991</v>
+        <v>130127001</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490910</v>
+        <v>490826</v>
       </c>
       <c r="R3" t="n">
-        <v>6679466</v>
+        <v>6679443</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,7 +859,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>8 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,49 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130127009</v>
+        <v>130126991</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490956</v>
+        <v>490910</v>
       </c>
       <c r="R4" t="n">
-        <v>6679462</v>
+        <v>6679466</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 bladrosetter 1 blomma.</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,7 +971,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130127001</v>
+        <v>130127009</v>
       </c>
       <c r="B5" t="n">
         <v>98949</v>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490826</v>
+        <v>490956</v>
       </c>
       <c r="R5" t="n">
-        <v>6679443</v>
+        <v>6679462</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2232,45 +2232,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130126987</v>
+        <v>130127011</v>
       </c>
       <c r="B17" t="n">
-        <v>91741</v>
+        <v>98949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490761</v>
+        <v>491011</v>
       </c>
       <c r="R17" t="n">
-        <v>6679321</v>
+        <v>6679350</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2303,6 +2307,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,7 +2338,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130127011</v>
+        <v>130127000</v>
       </c>
       <c r="B18" t="n">
         <v>98949</v>
@@ -2364,14 +2373,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högberget, Dlr</t>
+          <t>Vändleberget O, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491011</v>
+        <v>490811</v>
       </c>
       <c r="R18" t="n">
-        <v>6679350</v>
+        <v>6679375</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2408,7 +2417,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter</t>
+          <t>25-tal bladrosetter + 5 blomstänglar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,6 +2426,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2435,49 +2445,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130127000</v>
+        <v>130126987</v>
       </c>
       <c r="B19" t="n">
-        <v>98949</v>
+        <v>91741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vändleberget O, Dlr</t>
+          <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490811</v>
+        <v>490761</v>
       </c>
       <c r="R19" t="n">
-        <v>6679375</v>
+        <v>6679321</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2512,18 +2518,12 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>25-tal bladrosetter + 5 blomstänglar</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59950-2025 artfynd.xlsx
+++ b/artfynd/A 59950-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130127005</v>
+        <v>1306596</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490864</v>
+        <v>491087</v>
       </c>
       <c r="R2" t="n">
-        <v>6679464</v>
+        <v>6679414</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2011-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2011-07-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>15 rosetter</t>
+          <t>inga spår av modernt skogsbruk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,65 +761,71 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130127001</v>
+        <v>130126986</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490826</v>
+        <v>490770</v>
       </c>
       <c r="R3" t="n">
-        <v>6679443</v>
+        <v>6679323</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8 bladrosetter</t>
+          <t>På liggande tunn asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130126991</v>
+        <v>130126987</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490910</v>
+        <v>490761</v>
       </c>
       <c r="R4" t="n">
-        <v>6679466</v>
+        <v>6679321</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130127009</v>
+        <v>130127013</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,35 +997,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490956</v>
+        <v>490955</v>
       </c>
       <c r="R5" t="n">
         <v>6679462</v>
@@ -1066,18 +1059,12 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 bladrosetter 1 blomma.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1096,49 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130126999</v>
+        <v>130126985</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490775</v>
+        <v>490789</v>
       </c>
       <c r="R6" t="n">
-        <v>6679337</v>
+        <v>6679344</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>12 bladrosetter två blommor.</t>
+          <t>Asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130126985</v>
+        <v>130126993</v>
       </c>
       <c r="B7" t="n">
-        <v>80218</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490789</v>
+        <v>490802</v>
       </c>
       <c r="R7" t="n">
-        <v>6679344</v>
+        <v>6679402</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1278,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Asp.</t>
+          <t>Asp rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,32 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130127013</v>
+        <v>130126989</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>80460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490955</v>
+        <v>490806</v>
       </c>
       <c r="R8" t="n">
-        <v>6679462</v>
+        <v>6679373</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1402,45 +1384,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130126984</v>
+        <v>130126983</v>
       </c>
       <c r="B9" t="n">
-        <v>56425</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490936</v>
+        <v>490692</v>
       </c>
       <c r="R9" t="n">
-        <v>6679471</v>
+        <v>6679308</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1473,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack på död tall ner mot roten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,45 +1494,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130126989</v>
+        <v>130126979</v>
       </c>
       <c r="B10" t="n">
-        <v>80342</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490806</v>
+        <v>490739</v>
       </c>
       <c r="R10" t="n">
-        <v>6679373</v>
+        <v>6679371</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1570,6 +1573,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på äldre tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130127012</v>
+        <v>130136460</v>
       </c>
       <c r="B11" t="n">
-        <v>57033</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,16 +1615,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1624,14 +1632,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1639,13 +1647,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490767</v>
+        <v>490964</v>
       </c>
       <c r="R11" t="n">
-        <v>6679313</v>
+        <v>6679422</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,17 +1677,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Kort obs, vingljud hördes.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,22 +1702,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130126995</v>
+        <v>130127012</v>
       </c>
       <c r="B12" t="n">
-        <v>80274</v>
+        <v>57132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,34 +1725,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490815</v>
+        <v>490767</v>
       </c>
       <c r="R12" t="n">
-        <v>6679423</v>
+        <v>6679313</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1777,6 +1793,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kort obs, vingljud hördes.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,49 +1824,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130127010</v>
+        <v>130126991</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490952</v>
+        <v>490910</v>
       </c>
       <c r="R13" t="n">
-        <v>6679459</v>
+        <v>6679466</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1882,7 +1899,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 bladrosetter</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1908,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1910,38 +1926,43 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130127002</v>
+        <v>130136373</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1949,13 +1970,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490831</v>
+        <v>490966</v>
       </c>
       <c r="R14" t="n">
-        <v>6679493</v>
+        <v>6679369</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1979,17 +2000,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 bladrosett.</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,60 +2021,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130127003</v>
+        <v>130126984</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>56522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490873</v>
+        <v>490936</v>
       </c>
       <c r="R15" t="n">
-        <v>6679499</v>
+        <v>6679471</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2091,11 +2104,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>25-tal 2*2 m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,53 +2130,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130126979</v>
+        <v>130126998</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490739</v>
+        <v>490732</v>
       </c>
       <c r="R16" t="n">
-        <v>6679371</v>
+        <v>6679370</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,7 +2208,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på äldre tall.</t>
+          <t>25-tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130127011</v>
+        <v>130126999</v>
       </c>
       <c r="B17" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491011</v>
+        <v>490775</v>
       </c>
       <c r="R17" t="n">
-        <v>6679350</v>
+        <v>6679337</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2311,7 +2314,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter</t>
+          <t>12 bladrosetter två blommor.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,6 +2323,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2341,7 +2345,7 @@
         <v>130127000</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,45 +2449,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130126987</v>
+        <v>130127001</v>
       </c>
       <c r="B19" t="n">
-        <v>91741</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490761</v>
+        <v>490826</v>
       </c>
       <c r="R19" t="n">
-        <v>6679321</v>
+        <v>6679443</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2518,12 +2526,18 @@
           <t>2025-12-12</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>8 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2542,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130127004</v>
+        <v>130127002</v>
       </c>
       <c r="B20" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,16 +2588,17 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490904</v>
+        <v>490831</v>
       </c>
       <c r="R20" t="n">
-        <v>6679448</v>
+        <v>6679493</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2620,7 +2635,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>5 rosetter</t>
+          <t>1 bladrosett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2629,6 +2644,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2647,53 +2663,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130126983</v>
+        <v>130127003</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490692</v>
+        <v>490873</v>
       </c>
       <c r="R21" t="n">
-        <v>6679308</v>
+        <v>6679499</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2730,7 +2741,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack på död tall ner mot roten.</t>
+          <t>25-tal 2*2 m</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2757,45 +2768,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130126994</v>
+        <v>130127004</v>
       </c>
       <c r="B22" t="n">
-        <v>80274</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490798</v>
+        <v>490904</v>
       </c>
       <c r="R22" t="n">
-        <v>6679401</v>
+        <v>6679448</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2828,6 +2842,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 rosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,45 +2873,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130126993</v>
+        <v>130127005</v>
       </c>
       <c r="B23" t="n">
-        <v>80314</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490802</v>
+        <v>490864</v>
       </c>
       <c r="R23" t="n">
-        <v>6679402</v>
+        <v>6679464</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2929,7 +2951,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Asp rikligt</t>
+          <t>15 rosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2956,45 +2978,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130126986</v>
+        <v>130127007</v>
       </c>
       <c r="B24" t="n">
-        <v>91741</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490770</v>
+        <v>490905</v>
       </c>
       <c r="R24" t="n">
-        <v>6679323</v>
+        <v>6679465</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3031,7 +3056,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På liggande tunn asplåga.</t>
+          <t>15-tal</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3058,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130127007</v>
+        <v>130127009</v>
       </c>
       <c r="B25" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,16 +3115,17 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490905</v>
+        <v>490956</v>
       </c>
       <c r="R25" t="n">
-        <v>6679465</v>
+        <v>6679462</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3136,7 +3162,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>15-tal</t>
+          <t>2 bladrosetter 1 blomma.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3145,6 +3171,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3163,10 +3190,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130126998</v>
+        <v>130127010</v>
       </c>
       <c r="B26" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,16 +3222,17 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490732</v>
+        <v>490952</v>
       </c>
       <c r="R26" t="n">
-        <v>6679370</v>
+        <v>6679459</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3241,7 +3269,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>25-tal bladrosetter.</t>
+          <t>2 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3250,6 +3278,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3268,43 +3297,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130136373</v>
+        <v>130127011</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3312,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490966</v>
+        <v>491011</v>
       </c>
       <c r="R27" t="n">
-        <v>6679369</v>
+        <v>6679350</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3342,12 +3366,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>25-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,75 +3385,66 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130136460</v>
+        <v>130126994</v>
       </c>
       <c r="B28" t="n">
-        <v>57852</v>
+        <v>80392</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490964</v>
+        <v>490798</v>
       </c>
       <c r="R28" t="n">
-        <v>6679422</v>
+        <v>6679401</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3448,17 +3468,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3473,15 +3488,112 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130126995</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Högberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490815</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6679423</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
